--- a/Server/婚礼.xlsx
+++ b/Server/婚礼.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>婚礼筹备进度</t>
   </si>
@@ -55,16 +55,22 @@
     <t>未完成</t>
   </si>
   <si>
-    <t>在临沧拍摄，订金1000，总价2999，套餐内容:</t>
+    <t>11.1在临沧拍摄，订金1000，总价2999，包含：结婚大字报、结婚用的服装及伴郎伴娘服装，使用期7天</t>
   </si>
   <si>
     <t>化妆</t>
   </si>
   <si>
-    <t>2026.2.10</t>
-  </si>
-  <si>
-    <t>在威信化妆，688</t>
+    <t>2026.2.10晚或2026.2.11早上</t>
+  </si>
+  <si>
+    <t>已预约，在上门化妆，688</t>
+  </si>
+  <si>
+    <t>摄影跟拍</t>
+  </si>
+  <si>
+    <t>和化妆一起，从开始化妆就开始拍摄</t>
   </si>
   <si>
     <t>车队</t>
@@ -73,70 +79,49 @@
     <t>2026.2.11</t>
   </si>
   <si>
-    <t>威信车队到三桃，车队通知还早，先不用急</t>
+    <t>委托杨冲，6辆车，每辆480红包+烟一包，花自己装</t>
   </si>
   <si>
     <t>司仪</t>
   </si>
   <si>
-    <t>倾向于自己弄一个司仪讲两句话就行</t>
-  </si>
-  <si>
-    <t>乐队</t>
-  </si>
-  <si>
-    <t>待议</t>
-  </si>
-  <si>
-    <t>红包</t>
-  </si>
-  <si>
-    <t>腊月(待定)</t>
-  </si>
-  <si>
-    <t>拿到人员名单，包红包</t>
-  </si>
-  <si>
-    <t>上台交换戒指</t>
+    <t>不用婚庆公司，提前请个主持人</t>
   </si>
   <si>
     <t>伴郎伴娘</t>
   </si>
   <si>
-    <t>跟拍</t>
-  </si>
-  <si>
-    <t>照片+视频</t>
+    <t>伴郎伴娘各一个，已确定</t>
   </si>
   <si>
     <t>去三桃订亲</t>
   </si>
   <si>
+    <t>腊月初(待定)</t>
+  </si>
+  <si>
+    <t>具体礼节待沟通：红包金额及个数待定，购买物品及数量待定；等他们给出名单及购买物品清单，就可以包红包及准备购买东西</t>
+  </si>
+  <si>
+    <t>酒店</t>
+  </si>
+  <si>
+    <t>老扎西</t>
+  </si>
+  <si>
+    <t>桌数及宴请名单未完成</t>
+  </si>
+  <si>
+    <t>娱乐</t>
+  </si>
+  <si>
+    <t>已商定场所，具体购买牌及大贰数量待定</t>
+  </si>
+  <si>
+    <t>购买物资</t>
+  </si>
+  <si>
     <t>待定</t>
-  </si>
-  <si>
-    <t>具体礼节待沟通：红包金额及个数待定，购买物品及数量待定，去三桃人数待定</t>
-  </si>
-  <si>
-    <t>酒店</t>
-  </si>
-  <si>
-    <t>老扎西</t>
-  </si>
-  <si>
-    <t>已完成</t>
-  </si>
-  <si>
-    <t>桌数及宴请名单未完成</t>
-  </si>
-  <si>
-    <t>娱乐</t>
-  </si>
-  <si>
-    <t>已商定场所，具体购买牌及大贰数量待定</t>
-  </si>
-  <si>
-    <t>购买物资</t>
   </si>
   <si>
     <t>各种需要购买的东西</t>
@@ -1079,7 +1064,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="20.5555555555556" customWidth="1"/>
@@ -1139,22 +1124,19 @@
       <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="3:6">
       <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
         <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -1168,7 +1150,7 @@
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -1182,119 +1164,83 @@
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6">
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="3:5">
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="10" spans="3:5">
+    <row r="10" spans="3:6">
       <c r="C10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="3:6">
       <c r="C11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="12" spans="3:6">
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" t="s">
+    <row r="17" spans="3:6">
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" t="s">
         <v>7</v>
       </c>
-      <c r="F12" t="s">
-        <v>28</v>
+      <c r="F17" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="13" spans="3:6">
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" t="s">
+    <row r="25" spans="3:6">
+      <c r="C25" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="14" spans="3:6">
-      <c r="C14" t="s">
+      <c r="D25" t="s">
         <v>33</v>
       </c>
-      <c r="D14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="E25" t="s">
         <v>7</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F25" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="3:6">
-      <c r="C20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="3:6">
-      <c r="C28" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
